--- a/ky/downloads/data-excel/5.5.2.xlsx
+++ b/ky/downloads/data-excel/5.5.2.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22755" windowHeight="7305"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -251,7 +251,7 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -302,6 +302,13 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -605,14 +612,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="36.5703125" customWidth="1"/>
     <col min="4" max="4" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="1:21" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>10</v>
       </c>
@@ -633,7 +640,7 @@
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:20" s="1" customFormat="1" ht="22.5">
+    <row r="2" spans="1:21" s="1" customFormat="1" ht="22.5">
       <c r="A2" s="16" t="s">
         <v>8</v>
       </c>
@@ -654,7 +661,7 @@
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1">
+    <row r="3" spans="1:21" ht="15.75" thickBot="1">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -670,8 +677,9 @@
       <c r="M3" s="3"/>
       <c r="N3" s="2"/>
       <c r="O3" s="18"/>
+      <c r="U3" s="22"/>
     </row>
-    <row r="4" spans="1:20" s="1" customFormat="1" ht="15.75" thickBot="1">
+    <row r="4" spans="1:21" s="1" customFormat="1" ht="15.75" thickBot="1">
       <c r="A4" s="11" t="s">
         <v>3</v>
       </c>
@@ -732,8 +740,11 @@
       <c r="T4" s="20">
         <v>2023</v>
       </c>
+      <c r="U4" s="23">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" s="1" customFormat="1" ht="27" customHeight="1" thickBot="1">
+    <row r="5" spans="1:21" s="1" customFormat="1" ht="27" customHeight="1" thickBot="1">
       <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
@@ -793,6 +804,9 @@
       </c>
       <c r="T5" s="21">
         <v>40</v>
+      </c>
+      <c r="U5" s="24">
+        <v>41.5</v>
       </c>
     </row>
   </sheetData>
